--- a/fotos-fondos/Objetos.xlsx
+++ b/fotos-fondos/Objetos.xlsx
@@ -10,8 +10,30 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author>tc={09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}</author>
+  </authors>
+  <commentList>
+    <comment authorId="0" xr:uid="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}" ref="D31">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	@jimenaf@fing.edu.uy tiene sentido?
+Asignado a jimenaf@fing.edu.uy
+Reply:
+	Si. Está bien
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="135">
   <si>
     <t>Id</t>
   </si>
@@ -47,18 +69,6 @@
   </si>
   <si>
     <t>Se utilizan para estudiar y desarrollar procesos de obtención de pectina a partir de residuos agroindustriales.</t>
-  </si>
-  <si>
-    <t>id3</t>
-  </si>
-  <si>
-    <t>Destilación osmótica</t>
-  </si>
-  <si>
-    <t>Equipo para concentrar extractos líquidos quitándoles el agua sin necesidad de aplicar calor.</t>
-  </si>
-  <si>
-    <t>no quedó en fondo</t>
   </si>
   <si>
     <t>id4</t>
@@ -149,7 +159,7 @@
     <t>Pipe</t>
   </si>
   <si>
-    <t>robot cuadrúpedo autónomo equipado con cámaras y sensores diseñado para inspección, patrullaje y exploración.</t>
+    <t>Robot cuadrúpedo autónomo equipado con cámaras y sensores diseñado para inspección, patrullaje y exploración.</t>
   </si>
   <si>
     <t>comp_id5</t>
@@ -158,7 +168,7 @@
     <t>Robotito</t>
   </si>
   <si>
-    <t>pequeño robot móvil circular con ruedas omnidireccionales, usado en investigación y aprendizaje de robótica.</t>
+    <t>Pequeño robot móvil circular con ruedas omnidireccionales, usado en investigación y aprendizaje de robótica.</t>
   </si>
   <si>
     <t>comp_id6</t>
@@ -167,7 +177,7 @@
     <t>Jacky</t>
   </si>
   <si>
-    <t>robot móvil con ruedas, sensores y cámaras, usado para investigación, mapeo y navegación autónoma en terrenos variados.</t>
+    <t>Robot móvil con ruedas, sensores y cámaras, usado para investigación, mapeo y navegación autónoma en terrenos variados.</t>
   </si>
   <si>
     <t>naval_id1</t>
@@ -179,7 +189,7 @@
     <t>miscroscopio óptico</t>
   </si>
   <si>
-    <t>equipo que analiza la estructura, corrosión y desgaste de los metales y materiales de los barcos.</t>
+    <t>Equipo que analiza la estructura, corrosión y desgaste de los metales y materiales de los barcos.</t>
   </si>
   <si>
     <t>naval</t>
@@ -194,7 +204,7 @@
     <t>Brazo robot</t>
   </si>
   <si>
-    <t>robot articulado que realiza movimientos controlados para manipular objetos y probar tareas de automatización.</t>
+    <t>Robot articulado que realiza movimientos controlados para manipular objetos y probar tareas de automatización.</t>
   </si>
   <si>
     <t>mecanica</t>
@@ -218,95 +228,224 @@
     <t>celda electroquímica</t>
   </si>
   <si>
-    <t>celda electroquímica transparente con electrodos y cables, usada en laboratorio para evaluar propiedades químicas y energéticas de materiales.</t>
+    <t>Celda electroquímica transparente con electrodos y cables, usada en laboratorio para evaluar propiedades químicas y energéticas de materiales.</t>
+  </si>
+  <si>
+    <t>civil_id2</t>
   </si>
   <si>
     <t>Ingeniería Civil</t>
   </si>
   <si>
-    <t>Sistema de columnas de permeación</t>
-  </si>
-  <si>
-    <t>Equipo que simula el paso del agua por el suelo para estudiar el movimiento de contaminantes.</t>
-  </si>
-  <si>
-    <t>Máquina de ensayo de compresión para hormigón</t>
-  </si>
-  <si>
-    <t>Prensa de compresión que mide la resistencia del hormigón para evaluar su calidad y desempeño en obras de construcción.</t>
-  </si>
-  <si>
     <t>Transductores ultrasónicos</t>
   </si>
   <si>
-    <t>sensores que envían y reciben ondas de ultrasonido a través del hormigón para estudiar su interior sin romperlo y detectar poros o irregularidades.</t>
+    <t>Sensores que envían y reciben ondas de ultrasonido a través del hormigón para estudiar su interior sin romperlo y detectar poros o irregularidades.</t>
+  </si>
+  <si>
+    <t>civil</t>
+  </si>
+  <si>
+    <t>civil_id3</t>
   </si>
   <si>
     <t>Prensa de ensayo para mezclas asfálticas</t>
   </si>
   <si>
-    <t>equipo que aplica cargas controladas a muestras de asfalto para evaluar su resistencia y comportamiento, ayudando a diseñar pavimentos más seguros y duraderos.</t>
+    <t>Equipo que aplica cargas controladas a muestras de asfalto para evaluar su resistencia y comportamiento, ayudando a diseñar pavimentos más seguros y duraderos.</t>
+  </si>
+  <si>
+    <t>civil_id4</t>
   </si>
   <si>
     <t>Hormigonera</t>
   </si>
   <si>
-    <t>equipo que mezcla cemento, agua y áridos para producir hormigón de forma uniforme, asegurando una buena calidad para su uso en construcción.</t>
-  </si>
-  <si>
-    <t>Comparador de longitud</t>
-  </si>
-  <si>
-    <t>equipo que mide pequeñas expansiones o deformaciones en muestras de hormigón, ayudando a detectar procesos de deterioro y evaluar su durabilidad a lo largo del tiempo.</t>
+    <t>Equipo que mezcla cemento, agua y áridos para producir hormigón de forma uniforme, asegurando una buena calidad para su uso en construcción.</t>
+  </si>
+  <si>
+    <t>civil_id1</t>
   </si>
   <si>
     <t>Sensor de temperatura para hormigón</t>
   </si>
   <si>
-    <t>monitorea el hormigón durante su fraguado y ayuda a estimar cuándo alcanza la resistencia necesaria.</t>
-  </si>
-  <si>
-    <t>Probador de integridad de pilotes</t>
-  </si>
-  <si>
-    <t>equipo que verifica la calidad de fundaciones profundas mediante ondas generadas por un golpe de martillo.</t>
-  </si>
-  <si>
-    <t>Molde de ensayo para hormigón permeable</t>
-  </si>
-  <si>
-    <t>se utiliza para preparar muestras que permiten estudiar cómo el agua atraviesa el material y verificar que tenga la resistencia necesaria para pavimentos y estacionamientos.</t>
+    <t>Monitorea el hormigón durante su fraguado y ayuda a estimar cuándo alcanza la resistencia necesaria.</t>
+  </si>
+  <si>
+    <t>forest_id1</t>
+  </si>
+  <si>
+    <t>Ingeniería Forestal</t>
+  </si>
+  <si>
+    <t>forestal</t>
+  </si>
+  <si>
+    <t>forest_id2</t>
+  </si>
+  <si>
+    <t>Medidor digital de humedad y calibre</t>
+  </si>
+  <si>
+    <t>forest_id3</t>
+  </si>
+  <si>
+    <t>Balanza analítica de precisión con protector de vidrio</t>
+  </si>
+  <si>
+    <t>Balanza analítica empleada para determinar con exactitud el peso de reactivos secos, biopolímeros, catalizadores y muestras en estudios de rendimiento de procesos forestales</t>
+  </si>
+  <si>
+    <t>fm_id1</t>
+  </si>
+  <si>
+    <t>Ing. Físico - Matemática</t>
+  </si>
+  <si>
+    <t>Fotómetro solar</t>
+  </si>
+  <si>
+    <t>Sistema óptico de seguimiento solar utilizado para medir aerosoles y gases atmosféricos mediante técnicas de sensado remoto.</t>
+  </si>
+  <si>
+    <t>fisico-matematica</t>
+  </si>
+  <si>
+    <t>fm_id2</t>
+  </si>
+  <si>
+    <t>Prisma óptico</t>
+  </si>
+  <si>
+    <t>Elemento que descompone la luz blanca en los colores del arcoíris, ayudando a entender cómo se comporta la luz y la materia.</t>
+  </si>
+  <si>
+    <t>fm_id3</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Instrumento de medición electrónico que sirve para analizar magnitudes en circuitos eléctricos</t>
+  </si>
+  <si>
+    <t>prod_id1</t>
+  </si>
+  <si>
+    <t>Ing. Producción</t>
+  </si>
+  <si>
+    <t>Tablero Kanban</t>
+  </si>
+  <si>
+    <t>Herramienta visual que organiza tareas y flujos de trabajo para planificar la producción, evitar cuellos de botella y reducir desperdicios.</t>
+  </si>
+  <si>
+    <t>producción</t>
+  </si>
+  <si>
+    <t>prod_id2</t>
+  </si>
+  <si>
+    <t>Lote de envases con etiqueta de trazabilidad</t>
+  </si>
+  <si>
+    <t>Envases de producto terminado identificados con número de lote, que permiten rastrear su origen, las materias primas usadas y los controles de calidad realizados en cada etapa de producción.</t>
+  </si>
+  <si>
+    <t>ag_id1</t>
   </si>
   <si>
     <t>Agrimensura</t>
   </si>
   <si>
-    <t>Sistemas de comunicación</t>
-  </si>
-  <si>
-    <t>Electrica</t>
-  </si>
-  <si>
-    <t>Ingeniería Físico-Matemática</t>
-  </si>
-  <si>
-    <t>2 de fisica</t>
-  </si>
-  <si>
-    <t>Forestal</t>
-  </si>
-  <si>
-    <t>Producción</t>
-  </si>
-  <si>
-    <t>mec + quim + comp</t>
+    <t>Receptor GNSS</t>
+  </si>
+  <si>
+    <t>Antena de posicionamiento satelital de alta precisión que determina coordenadas en el terreno con bajo margen de error.</t>
+  </si>
+  <si>
+    <t>agrimensura</t>
+  </si>
+  <si>
+    <t>ag_id2</t>
+  </si>
+  <si>
+    <t>Estación total</t>
+  </si>
+  <si>
+    <t>Equipo óptico-electrónico que mide ángulos y distancias con gran precisión para relevar terrenos, delimitar predios y apoyar obras de construcción.</t>
+  </si>
+  <si>
+    <t>sc_id1</t>
+  </si>
+  <si>
+    <t>Sist. de comunicación</t>
+  </si>
+  <si>
+    <t>Radio definida por software (SDR)</t>
+  </si>
+  <si>
+    <t>Dispositivo que recibe y transmite señales de radio procesándolas por software, usado para experimentar con comunicaciones inalámbricas.</t>
+  </si>
+  <si>
+    <t>sistemas de comunicación</t>
+  </si>
+  <si>
+    <t>Bobina de fibra óptica</t>
+  </si>
+  <si>
+    <t>Cable de vidrio o plástico transparente que transmite información mediante pulsos de luz a gran velocidad, utilizado en las redes de internet y telecomunicaciones.</t>
+  </si>
+  <si>
+    <t>sc_id3</t>
+  </si>
+  <si>
+    <t>Analizador de espectro</t>
+  </si>
+  <si>
+    <t>Instrumento que muestra las señales de radio presentes en el aire, permitiendo estudiar frecuencias, interferencias y calidad de transmisión.</t>
+  </si>
+  <si>
+    <t>el_id1</t>
+  </si>
+  <si>
+    <t>Eléctrica</t>
+  </si>
+  <si>
+    <t>Osciloscopio</t>
+  </si>
+  <si>
+    <t>Instrumento que muestra gráficamente cómo varían las señales eléctricas en el tiempo, clave para analizar y diagnosticar circuitos.</t>
+  </si>
+  <si>
+    <t>electrica</t>
+  </si>
+  <si>
+    <t>el_id2</t>
+  </si>
+  <si>
+    <t>Motor de inducción</t>
+  </si>
+  <si>
+    <t>Máquina que transforma energía eléctrica en movimiento, usada para estudiar el funcionamiento y control de motores industriales.</t>
+  </si>
+  <si>
+    <t>el_id3</t>
+  </si>
+  <si>
+    <t>Panel solar fotovoltaico</t>
+  </si>
+  <si>
+    <t>Dispositivo que convierte la luz del sol en electricidad, utilizado para la generación de energía renovable y su integración a la red.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -329,10 +468,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -344,7 +479,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,20 +488,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAD1DC"/>
-        <bgColor rgb="FFEAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB7B7B7"/>
         <bgColor rgb="FFB7B7B7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF9900"/>
-        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -376,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -398,21 +521,8 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -421,11 +531,17 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,12 +551,42 @@
 </styleSheet>
 </file>
 
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{85b5e2ca-4c41-4393-858f-4c80d252c2ce}">
+    <Anchor>
+      <Comment id="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}"/>
+    </Anchor>
+    <History>
+      <Event time="2026-10-09T19:54:06.00" id="{60f08146-ea06-45d7-8513-523361aa99fb}">
+        <Attribution userId="placeholder@email.com" userName="Mercedes Marzoa Tanco" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2026-10-09T19:54:06.00" id="{cef14e4e-a76f-4cda-ac1b-40e305bf78df}">
+        <Attribution userId="placeholder@email.com" userName="Mercedes Marzoa Tanco" userProvider="google-sheets"/>
+        <Anchor>
+          <Comment id="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}"/>
+        </Anchor>
+        <Assign userId="jimenaf@fing.edu.uy" userName="jimenaf@fing.edu.uy" userProvider="google-sheets"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <x18tc:person displayName="jimenaf@fing.edu.uy" id="{923ab623-c180-4853-a39f-b7fb9b02d9f6}" userId="jimenaf@fing.edu.uy" providerId="google-sheets"/>
+  <x18tc:person displayName="Mercedes Marzoa Tanco" id="{19e0399b-323a-4756-8af6-16c70bdf585c}" providerId="google-sheets"/>
+  <x18tc:person displayName="J Ferreira" id="{0c794d68-75f8-4c7e-9c12-9afbe70929a0}" providerId="google-sheets"/>
+</x18tc:personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,6 +783,21 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <x18tc:threadedComment ref="D31" dT="2026-10-09T19:54:06.00" personId="{19e0399b-323a-4756-8af6-16c70bdf585c}" id="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}" done="1">
+    <x18tc:text xml:space="preserve">@jimenaf@fing.edu.uy tiene sentido?
+Asignado a jimenaf@fing.edu.uy</x18tc:text>
+    <x18tc:mentions>
+      <x18tc:mention mentionpersonId="{923ab623-c180-4853-a39f-b7fb9b02d9f6}" mentionId="{fb6ac457-68f5-46a4-bac1-5c0c5a246363}" startIndex="0" length="20"/>
+    </x18tc:mentions>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="D31" dT="2026-10-09T21:41:05.00" personId="{0c794d68-75f8-4c7e-9c12-9afbe70929a0}" id="{8f2242b3-6be3-4fb8-8d98-49062f7a2bcd}" parentId="{09a6cefd-a07b-4b3e-b784-6e6269b9b2ba}">
+    <x18tc:text xml:space="preserve">Si. Está bien</x18tc:text>
+  </x18tc:threadedComment>
+</x18tc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -696,442 +857,644 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="6" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="s">
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="14" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="6" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="s">
-        <v>32</v>
+      <c r="A12" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="6" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
+      <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="15" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
+      <c r="B14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="5" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
+      <c r="B15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="14" t="s">
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="s">
+      <c r="B16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="14" t="s">
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
+      <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D18" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="11" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="C20" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="D20" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="s">
-        <v>57</v>
+      <c r="A21" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="14" t="s">
+    </row>
+    <row r="23">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="s">
+      <c r="B24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D24" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="E24" s="6" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="B25" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="14" t="s">
         <v>71</v>
       </c>
+      <c r="D25" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26">
+      <c r="A26" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="B26" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="B27" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29">
-      <c r="B29" s="4" t="s">
-        <v>69</v>
+      <c r="A29" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="A30" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>81</v>
+      <c r="C30" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>83</v>
+      <c r="A31" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>85</v>
-      </c>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33">
-      <c r="B33" s="4" t="s">
-        <v>69</v>
+      <c r="A33" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+      <c r="A34" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="17" t="s">
+      <c r="A35" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="C35" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="17" t="s">
-        <v>89</v>
-      </c>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
     </row>
     <row r="37">
-      <c r="B37" s="17" t="s">
-        <v>90</v>
+      <c r="A37" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>92</v>
+      <c r="A38" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
     </row>
     <row r="40">
-      <c r="B40" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>95</v>
-      </c>
+      <c r="A40" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="4"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="4"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E2"/>
-    <hyperlink r:id="rId2" ref="E7"/>
-    <hyperlink r:id="rId3" ref="E12"/>
-    <hyperlink r:id="rId4" ref="E19"/>
-    <hyperlink r:id="rId5" ref="E21"/>
+    <hyperlink r:id="rId4" ref="E2"/>
+    <hyperlink r:id="rId5" ref="E6"/>
+    <hyperlink r:id="rId6" ref="E11"/>
+    <hyperlink r:id="rId7" ref="E18"/>
+    <hyperlink r:id="rId8" ref="E20"/>
+    <hyperlink r:id="rId9" ref="E24"/>
+    <hyperlink r:id="rId10" ref="E29"/>
+    <hyperlink r:id="rId11" ref="E33"/>
+    <hyperlink r:id="rId12" ref="E37"/>
+    <hyperlink r:id="rId13" ref="E40"/>
+    <hyperlink r:id="rId14" ref="E43"/>
+    <hyperlink r:id="rId15" ref="E47"/>
   </hyperlinks>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>